--- a/embod_mocap/my_data.xlsx
+++ b/embod_mocap/my_data.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>scene_folder</t>
   </si>
@@ -65,19 +65,19 @@
     <t>optim_scale</t>
   </si>
   <si>
-    <t>scene_20260413_113659</t>
+    <t>scene_20260413_161617</t>
   </si>
   <si>
     <t>seq0</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>()</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>scene_20260413_114638</t>
   </si>
 </sst>
 </file>
@@ -1071,8 +1071,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -1123,68 +1123,30 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>14</v>
-      </c>
       <c r="L2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" t="b">
         <v>0</v>
       </c>
     </row>
